--- a/data/dividends_info_20261029.xlsx
+++ b/data/dividends_info_20261029.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.18999862670898</v>
+        <v>44.20500183105469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2083815764336315</v>
+        <v>0.2035968697478339</v>
       </c>
       <c r="J2" t="n">
         <v>137</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>60.79999923706055</v>
+        <v>60.59999847412109</v>
       </c>
       <c r="I3" t="n">
-        <v>1.151315803920793</v>
+        <v>1.15511554063641</v>
       </c>
       <c r="J3" t="n">
         <v>116</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>8.600000381469727</v>
+        <v>8.659999847412109</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6976743876579468</v>
+        <v>0.6928406588590178</v>
       </c>
       <c r="J4" t="n">
         <v>46</v>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.5249999761581421</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7619047965051923</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J5" t="n">
         <v>46</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.18999862670898</v>
+        <v>44.20500183105469</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2083815764336315</v>
+        <v>0.2035968697478339</v>
       </c>
       <c r="J6" t="n">
         <v>46</v>
@@ -758,10 +758,10 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>26.93499946594238</v>
+        <v>26.88999938964844</v>
       </c>
       <c r="I7" t="n">
-        <v>1.707815144313038</v>
+        <v>1.710673151510303</v>
       </c>
       <c r="J7" t="n">
         <v>39</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>1.927999973297119</v>
+        <v>1.924000024795532</v>
       </c>
       <c r="I8" t="n">
-        <v>3.993775988923923</v>
+        <v>4.002078950502246</v>
       </c>
       <c r="J8" t="n">
         <v>25</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>52.90000152587891</v>
+        <v>52.84999847412109</v>
       </c>
       <c r="I9" t="n">
-        <v>0.6251417589056593</v>
+        <v>0.6257332252562561</v>
       </c>
       <c r="J9" t="n">
         <v>25</v>
@@ -899,10 +899,10 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>26.93499946594238</v>
+        <v>26.88999938964844</v>
       </c>
       <c r="I10" t="n">
-        <v>1.002413236879392</v>
+        <v>1.004090762843004</v>
       </c>
       <c r="J10" t="n">
         <v>25</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>27.55999946594238</v>
+        <v>27.3700008392334</v>
       </c>
       <c r="I11" t="n">
-        <v>2.140783786041433</v>
+        <v>2.155644800544789</v>
       </c>
       <c r="J11" t="n">
         <v>25</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>10</v>
+        <v>10.0600004196167</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>2.087475062033857</v>
       </c>
       <c r="J12" t="n">
         <v>18</v>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>8.069999694824219</v>
+        <v>8.010000228881836</v>
       </c>
       <c r="I15" t="n">
-        <v>0.7434944519078687</v>
+        <v>0.7490636490078573</v>
       </c>
       <c r="J15" t="n">
         <v>11</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.805000305175781</v>
+        <v>9.694999694824219</v>
       </c>
       <c r="I16" t="n">
-        <v>4.69148379074684</v>
+        <v>4.744713919336955</v>
       </c>
       <c r="J16" t="n">
         <v>-3</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>8.199999809265137</v>
+        <v>7.349999904632568</v>
       </c>
       <c r="I17" t="n">
-        <v>0.7317073340929389</v>
+        <v>0.8163265412042129</v>
       </c>
       <c r="J17" t="n">
         <v>-10</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.5249999761581421</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I18" t="n">
-        <v>0.7619047965051923</v>
+        <v>0.784313740156468</v>
       </c>
       <c r="J18" t="n">
         <v>-10</v>
@@ -1844,7 +1844,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1871,14 +1871,14 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1888,14 +1888,14 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1912,7 +1912,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1997,7 +1997,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2014,7 +2014,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2024,7 +2024,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2041,14 +2041,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2075,14 +2075,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2099,7 +2099,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2143,14 +2143,14 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2160,14 +2160,14 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2184,7 +2184,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2218,7 +2218,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2228,14 +2228,14 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2252,7 +2252,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2279,14 +2279,14 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2303,7 +2303,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2320,7 +2320,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2337,7 +2337,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2354,7 +2354,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2371,7 +2371,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2381,7 +2381,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2439,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2449,14 +2449,14 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2473,7 +2473,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2490,7 +2490,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2507,7 +2507,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2524,7 +2524,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2534,14 +2534,14 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2551,14 +2551,14 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2575,7 +2575,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2592,7 +2592,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2643,7 +2643,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -2660,7 +2660,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -2677,7 +2677,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -2687,14 +2687,14 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -2704,7 +2704,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -2762,7 +2762,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2779,7 +2779,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2796,7 +2796,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2806,14 +2806,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2823,14 +2823,14 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2847,7 +2847,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -2874,14 +2874,14 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2898,7 +2898,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2908,14 +2908,14 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2925,14 +2925,14 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -2949,7 +2949,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -2966,7 +2966,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -2976,14 +2976,14 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3000,7 +3000,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3010,14 +3010,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>RISANAMENTO S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3044,14 +3044,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>RISANAMENTO S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3061,14 +3061,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3085,7 +3085,7 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -3102,7 +3102,7 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3119,7 +3119,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>FOPE S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3136,7 +3136,7 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>FOPE S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -3153,7 +3153,7 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -3170,7 +3170,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -3187,7 +3187,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -3204,7 +3204,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -3238,7 +3238,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -3255,7 +3255,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -3265,14 +3265,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -3282,14 +3282,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -3299,14 +3299,14 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -3316,14 +3316,14 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3340,7 +3340,7 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -3350,14 +3350,14 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3374,7 +3374,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3391,7 +3391,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3408,7 +3408,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3418,14 +3418,14 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3442,7 +3442,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3459,7 +3459,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3469,14 +3469,14 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3493,7 +3493,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3503,14 +3503,14 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3527,7 +3527,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3544,7 +3544,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3561,7 +3561,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3578,7 +3578,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3588,14 +3588,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3605,14 +3605,14 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3629,7 +3629,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3663,7 +3663,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3673,14 +3673,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3697,7 +3697,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3714,7 +3714,7 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3724,14 +3724,14 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3748,7 +3748,7 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3782,7 +3782,7 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3799,7 +3799,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3816,7 +3816,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3826,14 +3826,14 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3843,14 +3843,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3867,7 +3867,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3877,14 +3877,14 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -3901,7 +3901,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -3918,7 +3918,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3935,7 +3935,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3945,14 +3945,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3962,14 +3962,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3986,7 +3986,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3996,14 +3996,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -4020,7 +4020,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -4037,7 +4037,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4047,14 +4047,14 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4064,14 +4064,14 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4088,7 +4088,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4105,7 +4105,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4115,14 +4115,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -4139,7 +4139,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -4149,14 +4149,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4173,7 +4173,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -4183,14 +4183,14 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -4207,7 +4207,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4224,7 +4224,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4234,14 +4234,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4258,7 +4258,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4275,7 +4275,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4292,7 +4292,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4302,14 +4302,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -4326,7 +4326,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4343,7 +4343,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4360,7 +4360,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -4377,7 +4377,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4394,7 +4394,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4428,7 +4428,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4445,7 +4445,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4462,7 +4462,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4472,14 +4472,14 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4496,7 +4496,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4506,14 +4506,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4530,7 +4530,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4547,7 +4547,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4564,7 +4564,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4581,7 +4581,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4598,7 +4598,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4615,7 +4615,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4625,14 +4625,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -4666,7 +4666,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -4683,7 +4683,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -4700,7 +4700,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4717,7 +4717,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4734,7 +4734,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4744,14 +4744,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4761,14 +4761,14 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -4785,7 +4785,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -4802,7 +4802,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -4812,14 +4812,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -4836,7 +4836,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -4853,7 +4853,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -4870,7 +4870,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -4880,14 +4880,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -4897,14 +4897,14 @@
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -4914,14 +4914,14 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -4931,14 +4931,14 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -4948,14 +4948,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -4972,7 +4972,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -4989,7 +4989,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5006,7 +5006,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5023,7 +5023,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -5040,7 +5040,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5091,7 +5091,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5108,7 +5108,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5125,7 +5125,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5142,7 +5142,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>Gens Aurea S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5152,14 +5152,14 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Gens Aurea S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -5169,14 +5169,14 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5193,7 +5193,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -5210,7 +5210,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>PIQUADRO S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5220,14 +5220,14 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>PIQUADRO S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5237,14 +5237,14 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5367,44 +5367,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Technoprobe S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-11-11</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>